--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/28.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/28.xlsx
@@ -426,13 +426,13 @@
         <v>-11.49145714547159</v>
       </c>
       <c r="E2">
-        <v>-17.29818861286138</v>
+        <v>-17.00569447670595</v>
       </c>
       <c r="F2">
-        <v>-4.519278626493617</v>
+        <v>-4.366544244765444</v>
       </c>
       <c r="G2">
-        <v>-12.18475281120524</v>
+        <v>-11.09756926580662</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.6503417814921</v>
       </c>
       <c r="E3">
-        <v>-17.98901637967951</v>
+        <v>-17.26802897597029</v>
       </c>
       <c r="F3">
-        <v>-4.375984319687747</v>
+        <v>-4.267240388885241</v>
       </c>
       <c r="G3">
-        <v>-11.7055008714543</v>
+        <v>-10.30008149066982</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.79293645254423</v>
       </c>
       <c r="E4">
-        <v>-18.34479141161812</v>
+        <v>-17.19995695468699</v>
       </c>
       <c r="F4">
-        <v>-4.471745248186175</v>
+        <v>-3.861030552104837</v>
       </c>
       <c r="G4">
-        <v>-12.03249428718233</v>
+        <v>-11.91888527190811</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.89015248622359</v>
       </c>
       <c r="E5">
-        <v>-18.15143462843861</v>
+        <v>-16.92860173519937</v>
       </c>
       <c r="F5">
-        <v>-4.281506532296254</v>
+        <v>-3.956644031205567</v>
       </c>
       <c r="G5">
-        <v>-12.39973844778006</v>
+        <v>-11.28619684959442</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.9537615753791</v>
       </c>
       <c r="E6">
-        <v>-17.86570603245064</v>
+        <v>-16.6920523669347</v>
       </c>
       <c r="F6">
-        <v>-4.061668592369503</v>
+        <v>-3.8699852037291</v>
       </c>
       <c r="G6">
-        <v>-12.27653842188758</v>
+        <v>-10.86431378758882</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.00059863972483</v>
       </c>
       <c r="E7">
-        <v>-19.11763889966317</v>
+        <v>-18.22176635825174</v>
       </c>
       <c r="F7">
-        <v>-3.703571162711096</v>
+        <v>-3.789433929113473</v>
       </c>
       <c r="G7">
-        <v>-12.53738897342032</v>
+        <v>-10.50449831260167</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.02970457109393</v>
       </c>
       <c r="E8">
-        <v>-20.17554476954306</v>
+        <v>-18.88806790984432</v>
       </c>
       <c r="F8">
-        <v>-3.559735931991198</v>
+        <v>-3.515379342673493</v>
       </c>
       <c r="G8">
-        <v>-12.21767002588959</v>
+        <v>-10.47365154872133</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.06734775317134</v>
       </c>
       <c r="E9">
-        <v>-20.00515640653046</v>
+        <v>-18.60813123211217</v>
       </c>
       <c r="F9">
-        <v>-3.237416518827105</v>
+        <v>-3.056047132718958</v>
       </c>
       <c r="G9">
-        <v>-11.7692320378034</v>
+        <v>-10.86094397304727</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.11885208388044</v>
       </c>
       <c r="E10">
-        <v>-21.85329910464485</v>
+        <v>-18.90067065300767</v>
       </c>
       <c r="F10">
-        <v>-2.929556258678877</v>
+        <v>-2.700622016301983</v>
       </c>
       <c r="G10">
-        <v>-11.64635029040219</v>
+        <v>-11.95735103224948</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.18688830924598</v>
       </c>
       <c r="E11">
-        <v>-21.63231863001855</v>
+        <v>-21.75406212524076</v>
       </c>
       <c r="F11">
-        <v>-3.197369096738763</v>
+        <v>-2.521525670347119</v>
       </c>
       <c r="G11">
-        <v>-11.59357840406164</v>
+        <v>-10.30713283580107</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.28405104147164</v>
       </c>
       <c r="E12">
-        <v>-21.34865048970407</v>
+        <v>-19.37000169916263</v>
       </c>
       <c r="F12">
-        <v>-2.922229349001115</v>
+        <v>-2.412910964859451</v>
       </c>
       <c r="G12">
-        <v>-11.95105764929847</v>
+        <v>-11.09089526115471</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.39182255803081</v>
       </c>
       <c r="E13">
-        <v>-21.91723210068514</v>
+        <v>-21.70351982684116</v>
       </c>
       <c r="F13">
-        <v>-2.524492054016544</v>
+        <v>-2.078573597415542</v>
       </c>
       <c r="G13">
-        <v>-11.5261296136857</v>
+        <v>-9.824881859544801</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.51600030044536</v>
       </c>
       <c r="E14">
-        <v>-23.21715773543097</v>
+        <v>-22.53804513087068</v>
       </c>
       <c r="F14">
-        <v>-2.195553985304083</v>
+        <v>-1.776376885200254</v>
       </c>
       <c r="G14">
-        <v>-11.27633677880829</v>
+        <v>-10.58105249280507</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.6379122157518</v>
       </c>
       <c r="E15">
-        <v>-24.52902042766101</v>
+        <v>-21.85099411137495</v>
       </c>
       <c r="F15">
-        <v>-2.013841655091178</v>
+        <v>-1.30552539814239</v>
       </c>
       <c r="G15">
-        <v>-10.40807633585583</v>
+        <v>-9.952924968459012</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.73605066662445</v>
       </c>
       <c r="E16">
-        <v>-23.73681371323316</v>
+        <v>-22.71314310685126</v>
       </c>
       <c r="F16">
-        <v>-1.697810378881735</v>
+        <v>-0.41443815743992</v>
       </c>
       <c r="G16">
-        <v>-10.02527262262321</v>
+        <v>-10.15910052514672</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.80024392702067</v>
       </c>
       <c r="E17">
-        <v>-24.90817144242721</v>
+        <v>-24.23226499746436</v>
       </c>
       <c r="F17">
-        <v>-0.9936318171099315</v>
+        <v>-1.471911274668699</v>
       </c>
       <c r="G17">
-        <v>-9.70127824340052</v>
+        <v>-9.088867770324198</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.79669357756124</v>
       </c>
       <c r="E18">
-        <v>-25.67664895305487</v>
+        <v>-25.20605899112578</v>
       </c>
       <c r="F18">
-        <v>-1.047264464604186</v>
+        <v>-0.7054775891069011</v>
       </c>
       <c r="G18">
-        <v>-9.606588751638064</v>
+        <v>-8.557401751897819</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.72049338159189</v>
       </c>
       <c r="E19">
-        <v>-26.42841186612021</v>
+        <v>-26.38468492110214</v>
       </c>
       <c r="F19">
-        <v>-0.5716680890630857</v>
+        <v>0.07394158386118171</v>
       </c>
       <c r="G19">
-        <v>-9.140999818460656</v>
+        <v>-8.728927608917791</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.55681804971382</v>
       </c>
       <c r="E20">
-        <v>-26.49772921775562</v>
+        <v>-25.02473889185866</v>
       </c>
       <c r="F20">
-        <v>-0.3227975284030163</v>
+        <v>0.8449205213621404</v>
       </c>
       <c r="G20">
-        <v>-10.09786636840436</v>
+        <v>-8.766901186025244</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.29874832889317</v>
       </c>
       <c r="E21">
-        <v>-27.46913217714098</v>
+        <v>-27.40517201025665</v>
       </c>
       <c r="F21">
-        <v>-0.3225556451213988</v>
+        <v>0.05144643867075834</v>
       </c>
       <c r="G21">
-        <v>-9.412488090289111</v>
+        <v>-8.625615066897115</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.96281646410816</v>
       </c>
       <c r="E22">
-        <v>-29.31547254260033</v>
+        <v>-25.51399975212137</v>
       </c>
       <c r="F22">
-        <v>0.1077596830804715</v>
+        <v>0.9258255088587625</v>
       </c>
       <c r="G22">
-        <v>-8.907711528027255</v>
+        <v>-7.423296738199144</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.55229898771449</v>
       </c>
       <c r="E23">
-        <v>-29.09977679714098</v>
+        <v>-27.1033945023855</v>
       </c>
       <c r="F23">
-        <v>0.01271280728325626</v>
+        <v>1.531247765603615</v>
       </c>
       <c r="G23">
-        <v>-8.769378508302626</v>
+        <v>-8.070133787877159</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.10179468890568</v>
       </c>
       <c r="E24">
-        <v>-30.47498604802732</v>
+        <v>-28.56618217634318</v>
       </c>
       <c r="F24">
-        <v>0.00792153022546392</v>
+        <v>1.777460095268101</v>
       </c>
       <c r="G24">
-        <v>-8.363186247794285</v>
+        <v>-7.180716028309396</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.63682429801745</v>
       </c>
       <c r="E25">
-        <v>-29.4517750817572</v>
+        <v>-28.25225930118345</v>
       </c>
       <c r="F25">
-        <v>0.6457122432347069</v>
+        <v>1.486045413167651</v>
       </c>
       <c r="G25">
-        <v>-8.860363500924468</v>
+        <v>-7.250018708866429</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.17933472561099</v>
       </c>
       <c r="E26">
-        <v>-30.31573999531059</v>
+        <v>-29.09010850513461</v>
       </c>
       <c r="F26">
-        <v>0.5287301986113607</v>
+        <v>1.851875652531191</v>
       </c>
       <c r="G26">
-        <v>-8.516891790524914</v>
+        <v>-8.337897873235645</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.763392419345948</v>
       </c>
       <c r="E27">
-        <v>-29.94897435695536</v>
+        <v>-29.30331811836374</v>
       </c>
       <c r="F27">
-        <v>0.213200913048015</v>
+        <v>1.58007836726384</v>
       </c>
       <c r="G27">
-        <v>-8.322951909032374</v>
+        <v>-8.296839947862313</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.3945874336911</v>
       </c>
       <c r="E28">
-        <v>-29.34575444828962</v>
+        <v>-27.25351341573977</v>
       </c>
       <c r="F28">
-        <v>0.02490886055467338</v>
+        <v>1.548923469244551</v>
       </c>
       <c r="G28">
-        <v>-8.311877786269248</v>
+        <v>-7.959438497347732</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.094618370430046</v>
       </c>
       <c r="E29">
-        <v>-29.83704632914477</v>
+        <v>-29.23844319972985</v>
       </c>
       <c r="F29">
-        <v>0.5228794396453877</v>
+        <v>0.8386945119626993</v>
       </c>
       <c r="G29">
-        <v>-8.274340611629201</v>
+        <v>-8.318686321005096</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.867865919280327</v>
       </c>
       <c r="E30">
-        <v>-28.96261384792265</v>
+        <v>-27.44004126011571</v>
       </c>
       <c r="F30">
-        <v>-0.05528621607774956</v>
+        <v>1.072186431789796</v>
       </c>
       <c r="G30">
-        <v>-8.212519116227703</v>
+        <v>-7.803944688867206</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.706346535254278</v>
       </c>
       <c r="E31">
-        <v>-29.40582465600137</v>
+        <v>-26.66796361265196</v>
       </c>
       <c r="F31">
-        <v>0.01876071769109545</v>
+        <v>1.128429264970271</v>
       </c>
       <c r="G31">
-        <v>-8.108238613846991</v>
+        <v>-7.616885528984823</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.613315826326838</v>
       </c>
       <c r="E32">
-        <v>-28.66802302830168</v>
+        <v>-27.76387696487823</v>
       </c>
       <c r="F32">
-        <v>0.06918095639729296</v>
+        <v>1.241536206883321</v>
       </c>
       <c r="G32">
-        <v>-8.929856492331947</v>
+        <v>-7.963300495123199</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.564105281385208</v>
       </c>
       <c r="E33">
-        <v>-28.40763124438662</v>
+        <v>-27.36373647308647</v>
       </c>
       <c r="F33">
-        <v>0.2626387080144923</v>
+        <v>1.154557629589373</v>
       </c>
       <c r="G33">
-        <v>-8.696056331335274</v>
+        <v>-7.408652646379342</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.549251320857067</v>
       </c>
       <c r="E34">
-        <v>-28.59717505245167</v>
+        <v>-26.25867560336471</v>
       </c>
       <c r="F34">
-        <v>-0.6272797062826277</v>
+        <v>1.151252443652203</v>
       </c>
       <c r="G34">
-        <v>-8.457764178023721</v>
+        <v>-8.626038344478284</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.55059369599892</v>
       </c>
       <c r="E35">
-        <v>-27.52759477658001</v>
+        <v>-26.42910019416937</v>
       </c>
       <c r="F35">
-        <v>-0.5706781900167404</v>
+        <v>0.8763173026630472</v>
       </c>
       <c r="G35">
-        <v>-7.862311057966609</v>
+        <v>-7.630450098911568</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.543060788560679</v>
       </c>
       <c r="E36">
-        <v>-27.85140331049848</v>
+        <v>-26.36263125268479</v>
       </c>
       <c r="F36">
-        <v>-0.2469066487955396</v>
+        <v>0.5403397677615958</v>
       </c>
       <c r="G36">
-        <v>-7.783847206815608</v>
+        <v>-7.444742802311675</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.521997470968408</v>
       </c>
       <c r="E37">
-        <v>-27.10084044304517</v>
+        <v>-25.97704980482769</v>
       </c>
       <c r="F37">
-        <v>-0.4151745760610088</v>
+        <v>0.779597124712177</v>
       </c>
       <c r="G37">
-        <v>-8.526069367226681</v>
+        <v>-7.976901158487097</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.467509614228725</v>
       </c>
       <c r="E38">
-        <v>-27.641535711087</v>
+        <v>-26.06770532598724</v>
       </c>
       <c r="F38">
-        <v>-0.7413152480542161</v>
+        <v>0.9622140321289392</v>
       </c>
       <c r="G38">
-        <v>-8.458745263269995</v>
+        <v>-6.966494916357929</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.378421791448638</v>
       </c>
       <c r="E39">
-        <v>-27.13376697755494</v>
+        <v>-24.34903169975214</v>
       </c>
       <c r="F39">
-        <v>-0.3761659266957773</v>
+        <v>0.5773570218904973</v>
       </c>
       <c r="G39">
-        <v>-8.990900338223858</v>
+        <v>-6.447100512048747</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.254599885407352</v>
       </c>
       <c r="E40">
-        <v>-26.28467810111675</v>
+        <v>-24.37456323620739</v>
       </c>
       <c r="F40">
-        <v>-0.4006060785479739</v>
+        <v>0.8433499367664326</v>
       </c>
       <c r="G40">
-        <v>-7.973957902748276</v>
+        <v>-6.672303872559675</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.091008973911629</v>
       </c>
       <c r="E41">
-        <v>-25.42609754315848</v>
+        <v>-23.43109190450133</v>
       </c>
       <c r="F41">
-        <v>-0.1903904543721405</v>
+        <v>0.4605066876841962</v>
       </c>
       <c r="G41">
-        <v>-8.469550325865246</v>
+        <v>-7.434141175453109</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.902927372797027</v>
       </c>
       <c r="E42">
-        <v>-25.12302036324713</v>
+        <v>-22.92485832365787</v>
       </c>
       <c r="F42">
-        <v>-0.210042642636156</v>
+        <v>-0.04931865730798192</v>
       </c>
       <c r="G42">
-        <v>-7.44849651977568</v>
+        <v>-7.476711743965344</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.691436508655904</v>
       </c>
       <c r="E43">
-        <v>-23.55820616989664</v>
+        <v>-23.90018294153388</v>
       </c>
       <c r="F43">
-        <v>-0.8116908574938537</v>
+        <v>0.3045590688005641</v>
       </c>
       <c r="G43">
-        <v>-7.960642705660049</v>
+        <v>-7.314265027000356</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.470142004706837</v>
       </c>
       <c r="E44">
-        <v>-24.31359639064212</v>
+        <v>-23.11134088329373</v>
       </c>
       <c r="F44">
-        <v>-0.4311778059156924</v>
+        <v>0.7455247167002277</v>
       </c>
       <c r="G44">
-        <v>-7.135707512178493</v>
+        <v>-6.923153260779224</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.253641845635414</v>
       </c>
       <c r="E45">
-        <v>-23.49912769799257</v>
+        <v>-21.95675209335008</v>
       </c>
       <c r="F45">
-        <v>-0.7033097516137748</v>
+        <v>0.3713321084054266</v>
       </c>
       <c r="G45">
-        <v>-7.777757259601279</v>
+        <v>-6.121688645112377</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.045333130139698</v>
       </c>
       <c r="E46">
-        <v>-21.82986425165516</v>
+        <v>-20.6854871705988</v>
       </c>
       <c r="F46">
-        <v>-0.5603559038104557</v>
+        <v>0.2481762415290157</v>
       </c>
       <c r="G46">
-        <v>-8.625218039088422</v>
+        <v>-7.216484624528904</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.86508739738971</v>
       </c>
       <c r="E47">
-        <v>-21.97242061341662</v>
+        <v>-21.38289933862409</v>
       </c>
       <c r="F47">
-        <v>-0.5554900736864115</v>
+        <v>0.2701230074987858</v>
       </c>
       <c r="G47">
-        <v>-9.128455708438899</v>
+        <v>-6.382913255902889</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.713559671265042</v>
       </c>
       <c r="E48">
-        <v>-21.88499842269854</v>
+        <v>-19.7732170248056</v>
       </c>
       <c r="F48">
-        <v>-0.5289384133244789</v>
+        <v>0.521168032591204</v>
       </c>
       <c r="G48">
-        <v>-7.788424510891033</v>
+        <v>-5.882658216949948</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.597387266788514</v>
       </c>
       <c r="E49">
-        <v>-20.15961359798408</v>
+        <v>-19.9383478294953</v>
       </c>
       <c r="F49">
-        <v>-0.5359646256350242</v>
+        <v>0.1761902858583359</v>
       </c>
       <c r="G49">
-        <v>-8.140558646207522</v>
+        <v>-6.383487469675792</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.521657175984931</v>
       </c>
       <c r="E50">
-        <v>-19.67955912537896</v>
+        <v>-20.10664403751636</v>
       </c>
       <c r="F50">
-        <v>-0.4881032138360745</v>
+        <v>0.6003632697684479</v>
       </c>
       <c r="G50">
-        <v>-7.93155795775713</v>
+        <v>-6.856964459482105</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.476336582585683</v>
       </c>
       <c r="E51">
-        <v>-20.31851775091323</v>
+        <v>-18.78629045652193</v>
       </c>
       <c r="F51">
-        <v>-0.6208341795214448</v>
+        <v>-0.2028491001102451</v>
       </c>
       <c r="G51">
-        <v>-7.950933571065652</v>
+        <v>-6.559603755657427</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.467514794019693</v>
       </c>
       <c r="E52">
-        <v>-19.74308455875856</v>
+        <v>-18.15900623697944</v>
       </c>
       <c r="F52">
-        <v>-0.6740335908640347</v>
+        <v>-0.01678369919562854</v>
       </c>
       <c r="G52">
-        <v>-7.495975795740844</v>
+        <v>-6.53991642630076</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.48364765686199</v>
       </c>
       <c r="E53">
-        <v>-18.60725270815468</v>
+        <v>-18.96366172645437</v>
       </c>
       <c r="F53">
-        <v>-0.815618975717929</v>
+        <v>-0.2715547208658389</v>
       </c>
       <c r="G53">
-        <v>-7.980910811232738</v>
+        <v>-6.80481928645941</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.517820821065174</v>
       </c>
       <c r="E54">
-        <v>-17.97470640181527</v>
+        <v>-18.02068852688915</v>
       </c>
       <c r="F54">
-        <v>-0.4293703082427839</v>
+        <v>-0.4410883935227857</v>
       </c>
       <c r="G54">
-        <v>-8.019314228364479</v>
+        <v>-5.207166259393302</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.566203392336825</v>
       </c>
       <c r="E55">
-        <v>-17.77853290780299</v>
+        <v>-17.62600937475064</v>
       </c>
       <c r="F55">
-        <v>-1.143842163361774</v>
+        <v>-0.8594984254116216</v>
       </c>
       <c r="G55">
-        <v>-8.077565754709301</v>
+        <v>-7.09766831063985</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.611673157947341</v>
       </c>
       <c r="E56">
-        <v>-18.05611930752517</v>
+        <v>-16.11623425448938</v>
       </c>
       <c r="F56">
-        <v>-0.8765835030943614</v>
+        <v>-0.1860854289797915</v>
       </c>
       <c r="G56">
-        <v>-7.94692391832001</v>
+        <v>-6.910448370901054</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.655051801776499</v>
       </c>
       <c r="E57">
-        <v>-17.69179904513408</v>
+        <v>-15.52246527107765</v>
       </c>
       <c r="F57">
-        <v>-0.8173403231809463</v>
+        <v>-0.1742778800202874</v>
       </c>
       <c r="G57">
-        <v>-8.883686423769001</v>
+        <v>-6.344034061645029</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.686215040758692</v>
       </c>
       <c r="E58">
-        <v>-16.75839451114707</v>
+        <v>-16.07603499072329</v>
       </c>
       <c r="F58">
-        <v>-0.9011147753608659</v>
+        <v>0.07417104163175718</v>
       </c>
       <c r="G58">
-        <v>-8.54286265916792</v>
+        <v>-7.169277689953172</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.7006589012498</v>
       </c>
       <c r="E59">
-        <v>-16.65049456096631</v>
+        <v>-14.39237099704149</v>
       </c>
       <c r="F59">
-        <v>-1.322158187223202</v>
+        <v>-1.151607279395617</v>
       </c>
       <c r="G59">
-        <v>-8.384839028865061</v>
+        <v>-6.140798479474583</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.70275716155282</v>
       </c>
       <c r="E60">
-        <v>-15.72821195914214</v>
+        <v>-14.28010106944332</v>
       </c>
       <c r="F60">
-        <v>-1.216428685399484</v>
+        <v>-0.220697932538366</v>
       </c>
       <c r="G60">
-        <v>-8.411262706083269</v>
+        <v>-7.494450027715703</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.68619014386501</v>
       </c>
       <c r="E61">
-        <v>-15.65905763257101</v>
+        <v>-16.37325685374272</v>
       </c>
       <c r="F61">
-        <v>-1.335412065667994</v>
+        <v>-0.6447706839927393</v>
       </c>
       <c r="G61">
-        <v>-8.682990507085565</v>
+        <v>-8.022290296318896</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.663718284674428</v>
       </c>
       <c r="E62">
-        <v>-15.12108397740779</v>
+        <v>-15.09393124725779</v>
       </c>
       <c r="F62">
-        <v>-1.229263409938459</v>
+        <v>0.3399817156790765</v>
       </c>
       <c r="G62">
-        <v>-8.842156002491109</v>
+        <v>-8.259968861198834</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.638299600571671</v>
       </c>
       <c r="E63">
-        <v>-15.1582853913808</v>
+        <v>-14.25772587937142</v>
       </c>
       <c r="F63">
-        <v>-1.551837960262615</v>
+        <v>-0.8728939546822924</v>
       </c>
       <c r="G63">
-        <v>-8.251670651874997</v>
+        <v>-7.567129085257403</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.613271225079387</v>
       </c>
       <c r="E64">
-        <v>-15.62369477904511</v>
+        <v>-14.70436021379994</v>
       </c>
       <c r="F64">
-        <v>-1.379473756190302</v>
+        <v>-0.5884350736631505</v>
       </c>
       <c r="G64">
-        <v>-9.30944460843631</v>
+        <v>-8.701893624489527</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.599519902537653</v>
       </c>
       <c r="E65">
-        <v>-14.04326187884216</v>
+        <v>-13.16931620857587</v>
       </c>
       <c r="F65">
-        <v>-1.416787565849406</v>
+        <v>-0.5758041275052637</v>
       </c>
       <c r="G65">
-        <v>-8.649807513454901</v>
+        <v>-9.573205603492273</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.59183724820344</v>
       </c>
       <c r="E66">
-        <v>-14.21677941739407</v>
+        <v>-12.5058585386601</v>
       </c>
       <c r="F66">
-        <v>-1.622835673621755</v>
+        <v>-0.1398459605555231</v>
       </c>
       <c r="G66">
-        <v>-9.038668361686254</v>
+        <v>-8.957061100281305</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.598291355314258</v>
       </c>
       <c r="E67">
-        <v>-15.3167457538572</v>
+        <v>-14.02430115817205</v>
       </c>
       <c r="F67">
-        <v>-1.81097199304337</v>
+        <v>-1.171046577237113</v>
       </c>
       <c r="G67">
-        <v>-8.28846627044261</v>
+        <v>-7.788099669956648</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.615405007527503</v>
       </c>
       <c r="E68">
-        <v>-14.19543219092191</v>
+        <v>-12.98016184927548</v>
       </c>
       <c r="F68">
-        <v>-1.768399707111295</v>
+        <v>-0.6436987765735168</v>
       </c>
       <c r="G68">
-        <v>-8.727231217371559</v>
+        <v>-8.211006473088799</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.63672574525363</v>
       </c>
       <c r="E69">
-        <v>-14.22223622857331</v>
+        <v>-13.80471545354011</v>
       </c>
       <c r="F69">
-        <v>-1.784137859397083</v>
+        <v>-0.497537490186558</v>
       </c>
       <c r="G69">
-        <v>-8.559829855851808</v>
+        <v>-8.991372834128418</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.663523747848442</v>
       </c>
       <c r="E70">
-        <v>-14.3455601612242</v>
+        <v>-14.30138036880536</v>
       </c>
       <c r="F70">
-        <v>-1.841266217331151</v>
+        <v>-1.558044088844389</v>
       </c>
       <c r="G70">
-        <v>-8.718211139304644</v>
+        <v>-8.921988123032399</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.681597438671551</v>
       </c>
       <c r="E71">
-        <v>-15.1712141846727</v>
+        <v>-13.01017657499832</v>
       </c>
       <c r="F71">
-        <v>-2.233723498490278</v>
+        <v>-1.089570844599962</v>
       </c>
       <c r="G71">
-        <v>-9.725001475275304</v>
+        <v>-8.205835267911114</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.691246244521954</v>
       </c>
       <c r="E72">
-        <v>-15.02570072938422</v>
+        <v>-13.44925741478203</v>
       </c>
       <c r="F72">
-        <v>-2.094403698483041</v>
+        <v>-1.308103277499902</v>
       </c>
       <c r="G72">
-        <v>-8.80486820068958</v>
+        <v>-7.691014886455798</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.686764273671091</v>
       </c>
       <c r="E73">
-        <v>-14.67205408022921</v>
+        <v>-14.20164978573444</v>
       </c>
       <c r="F73">
-        <v>-2.025102481564834</v>
+        <v>-1.072317608334454</v>
       </c>
       <c r="G73">
-        <v>-8.109472353153341</v>
+        <v>-8.607105696080287</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.662368175298912</v>
       </c>
       <c r="E74">
-        <v>-14.95483011116418</v>
+        <v>-14.24573448019911</v>
       </c>
       <c r="F74">
-        <v>-2.104568594882793</v>
+        <v>-1.461502838252523</v>
       </c>
       <c r="G74">
-        <v>-8.494727138890864</v>
+        <v>-8.16674279425189</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.622686123956965</v>
       </c>
       <c r="E75">
-        <v>-15.45671182848627</v>
+        <v>-14.63879696711688</v>
       </c>
       <c r="F75">
-        <v>-2.079042453365527</v>
+        <v>-1.114297611573527</v>
       </c>
       <c r="G75">
-        <v>-8.051952539216277</v>
+        <v>-7.13513657962715</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.559994509817338</v>
       </c>
       <c r="E76">
-        <v>-15.69333365233507</v>
+        <v>-14.82131258352203</v>
       </c>
       <c r="F76">
-        <v>-2.529093634939095</v>
+        <v>-1.844288101616564</v>
       </c>
       <c r="G76">
-        <v>-7.988615119454315</v>
+        <v>-8.023258256678933</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.479523461388825</v>
       </c>
       <c r="E77">
-        <v>-15.21137722064672</v>
+        <v>-14.49591455522687</v>
       </c>
       <c r="F77">
-        <v>-1.736111602484976</v>
+        <v>-2.27366737465327</v>
       </c>
       <c r="G77">
-        <v>-7.409627169182498</v>
+        <v>-7.291030697137928</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.380560044230068</v>
       </c>
       <c r="E78">
-        <v>-15.14880729528274</v>
+        <v>-15.81461071473448</v>
       </c>
       <c r="F78">
-        <v>-2.568890890071792</v>
+        <v>-1.57718020421646</v>
       </c>
       <c r="G78">
-        <v>-7.12190013185635</v>
+        <v>-7.11279802325045</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.260531973287478</v>
       </c>
       <c r="E79">
-        <v>-16.08593423490406</v>
+        <v>-13.89090137085409</v>
       </c>
       <c r="F79">
-        <v>-2.190109126365481</v>
+        <v>-1.723413558567462</v>
       </c>
       <c r="G79">
-        <v>-6.724445764360811</v>
+        <v>-7.058506931327878</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.127465681561311</v>
       </c>
       <c r="E80">
-        <v>-16.78344150088349</v>
+        <v>-15.71663717957854</v>
       </c>
       <c r="F80">
-        <v>-2.129914980673652</v>
+        <v>-2.222552964063527</v>
       </c>
       <c r="G80">
-        <v>-6.305377990453211</v>
+        <v>-6.648390329834442</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.977777023229651</v>
       </c>
       <c r="E81">
-        <v>-18.98642183681692</v>
+        <v>-15.67685906389516</v>
       </c>
       <c r="F81">
-        <v>-2.378143556596553</v>
+        <v>-1.618178592083216</v>
       </c>
       <c r="G81">
-        <v>-5.927797981943229</v>
+        <v>-4.603401805126118</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.81965742146602</v>
       </c>
       <c r="E82">
-        <v>-17.17554395131164</v>
+        <v>-15.89922978004181</v>
       </c>
       <c r="F82">
-        <v>-2.265246191636411</v>
+        <v>-2.00306873701777</v>
       </c>
       <c r="G82">
-        <v>-5.941963015415352</v>
+        <v>-5.430213857339676</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.656441676104045</v>
       </c>
       <c r="E83">
-        <v>-18.81963361064041</v>
+        <v>-19.0309276793643</v>
       </c>
       <c r="F83">
-        <v>-2.535706491915644</v>
+        <v>-2.059779597780827</v>
       </c>
       <c r="G83">
-        <v>-5.047994201544639</v>
+        <v>-4.888129805946933</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.487722188346736</v>
       </c>
       <c r="E84">
-        <v>-19.51730843015814</v>
+        <v>-18.93105671359914</v>
       </c>
       <c r="F84">
-        <v>-2.666992784850532</v>
+        <v>-1.906283118042079</v>
       </c>
       <c r="G84">
-        <v>-5.291113031770136</v>
+        <v>-5.221974412291076</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.323139505219181</v>
       </c>
       <c r="E85">
-        <v>-21.0801572657893</v>
+        <v>-19.15069675991917</v>
       </c>
       <c r="F85">
-        <v>-2.98277140900212</v>
+        <v>-2.257008906182972</v>
       </c>
       <c r="G85">
-        <v>-4.809744704113358</v>
+        <v>-4.755775171903611</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.15982243366442</v>
       </c>
       <c r="E86">
-        <v>-21.47679271869912</v>
+        <v>-20.19275297077221</v>
       </c>
       <c r="F86">
-        <v>-2.804832292308967</v>
+        <v>-2.018188098853666</v>
       </c>
       <c r="G86">
-        <v>-5.048240293161597</v>
+        <v>-4.247103799650694</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.005646004449599</v>
       </c>
       <c r="E87">
-        <v>-22.00403841893818</v>
+        <v>-21.05900929217348</v>
       </c>
       <c r="F87">
-        <v>-2.995607790275901</v>
+        <v>-2.526943193161427</v>
       </c>
       <c r="G87">
-        <v>-4.66909842318932</v>
+        <v>-4.781171826773713</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.865684082340108</v>
       </c>
       <c r="E88">
-        <v>-23.82641409994893</v>
+        <v>-23.31356894705427</v>
       </c>
       <c r="F88">
-        <v>-2.895526925771873</v>
+        <v>-2.191444454618794</v>
       </c>
       <c r="G88">
-        <v>-5.446157312897017</v>
+        <v>-4.84997248043215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.739371068106145</v>
       </c>
       <c r="E89">
-        <v>-25.23119655034236</v>
+        <v>-22.78032301875505</v>
       </c>
       <c r="F89">
-        <v>-3.151632447327994</v>
+        <v>-1.873582486449165</v>
       </c>
       <c r="G89">
-        <v>-4.711104621593331</v>
+        <v>-4.075728878822456</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.639376746703864</v>
       </c>
       <c r="E90">
-        <v>-26.47206635555415</v>
+        <v>-24.79826537826105</v>
       </c>
       <c r="F90">
-        <v>-3.181117356663239</v>
+        <v>-2.624389849324553</v>
       </c>
       <c r="G90">
-        <v>-4.553612549183104</v>
+        <v>-3.290050220078097</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.565695696942453</v>
       </c>
       <c r="E91">
-        <v>-28.31248800548547</v>
+        <v>-27.55967448645035</v>
       </c>
       <c r="F91">
-        <v>-3.070296708781916</v>
+        <v>-2.786956952123956</v>
       </c>
       <c r="G91">
-        <v>-4.75732390847967</v>
+        <v>-3.822175764037925</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.526013482283848</v>
       </c>
       <c r="E92">
-        <v>-29.86759315056351</v>
+        <v>-28.28829236886249</v>
       </c>
       <c r="F92">
-        <v>-3.32534689026687</v>
+        <v>-2.154054435158633</v>
       </c>
       <c r="G92">
-        <v>-4.792675789561127</v>
+        <v>-4.007663218793335</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.527357915389577</v>
       </c>
       <c r="E93">
-        <v>-31.53125261031643</v>
+        <v>-29.43664545009757</v>
       </c>
       <c r="F93">
-        <v>-3.305523229950475</v>
+        <v>-2.451729089722038</v>
       </c>
       <c r="G93">
-        <v>-4.707944805231586</v>
+        <v>-4.618666047820654</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.566277520415802</v>
       </c>
       <c r="E94">
-        <v>-32.75546442389101</v>
+        <v>-31.45533500781484</v>
       </c>
       <c r="F94">
-        <v>-3.620675608345546</v>
+        <v>-2.828344672670028</v>
       </c>
       <c r="G94">
-        <v>-4.618088552826192</v>
+        <v>-4.147748410830708</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.650955646968841</v>
       </c>
       <c r="E95">
-        <v>-34.67856015954336</v>
+        <v>-32.2226985138366</v>
       </c>
       <c r="F95">
-        <v>-3.68272943885666</v>
+        <v>-3.226878028728689</v>
       </c>
       <c r="G95">
-        <v>-5.890178776764195</v>
+        <v>-5.1437107156552</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.775824024438727</v>
       </c>
       <c r="E96">
-        <v>-36.3950759679138</v>
+        <v>-36.97893665019675</v>
       </c>
       <c r="F96">
-        <v>-4.085236473346551</v>
+        <v>-3.333919664518441</v>
       </c>
       <c r="G96">
-        <v>-5.411858703936142</v>
+        <v>-4.772916273330151</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.934360154378643</v>
       </c>
       <c r="E97">
-        <v>-39.13256341215758</v>
+        <v>-38.99544348344232</v>
       </c>
       <c r="F97">
-        <v>-4.492371596515883</v>
+        <v>-3.14015955879922</v>
       </c>
       <c r="G97">
-        <v>-6.591707227395035</v>
+        <v>-5.345384436363351</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.124689427573673</v>
       </c>
       <c r="E98">
-        <v>-39.7966980889375</v>
+        <v>-40.33006402179791</v>
       </c>
       <c r="F98">
-        <v>-3.845237727570464</v>
+        <v>-3.356505930123173</v>
       </c>
       <c r="G98">
-        <v>-6.166726692237315</v>
+        <v>-5.339934327353114</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.323495787768158</v>
       </c>
       <c r="E99">
-        <v>-43.06729334302324</v>
+        <v>-41.93990709644368</v>
       </c>
       <c r="F99">
-        <v>-4.394506614814344</v>
+        <v>-3.7084842097771</v>
       </c>
       <c r="G99">
-        <v>-7.268275425623179</v>
+        <v>-6.249420037978441</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.533135986393591</v>
       </c>
       <c r="E100">
-        <v>-45.15049101297978</v>
+        <v>-44.44319545043276</v>
       </c>
       <c r="F100">
-        <v>-4.060175874309658</v>
+        <v>-3.749019540265691</v>
       </c>
       <c r="G100">
-        <v>-7.614838046731729</v>
+        <v>-5.017029313688159</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.720054928112133</v>
       </c>
       <c r="E101">
-        <v>-46.97192024292293</v>
+        <v>-46.67291642538147</v>
       </c>
       <c r="F101">
-        <v>-4.04595280600359</v>
+        <v>-4.097381167838995</v>
       </c>
       <c r="G101">
-        <v>-8.083458828630064</v>
+        <v>-6.669879049827246</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.891525249448306</v>
       </c>
       <c r="E102">
-        <v>-49.50644714273542</v>
+        <v>-49.89925490299026</v>
       </c>
       <c r="F102">
-        <v>-4.379187616434373</v>
+        <v>-4.058683156249813</v>
       </c>
       <c r="G102">
-        <v>-8.01771955468659</v>
+        <v>-6.08338038340586</v>
       </c>
     </row>
   </sheetData>
